--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0084.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0084.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Hãy tiếp tục khám phá</t>
+          <t>Hãy tiếp tục khám phá nào</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Bạn chưa đạt Cấp Độ Liên Minh yêu cầu</t>
+          <t>Bạn chưa đạt Cấp Độ Liên Minh yêu cầu.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Chính tiên quyết để mở khóa</t>
+          <t>Hoàn thành các Nhiệm vụ chính tiên quyết để mở khóa</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Đã hoàn thành tất cả Nhiệm Vụ Chính có sẵn</t>
+          <t>Tất cả Nhiệm Vụ Chính hiện có đã hoàn thành.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Đã hoàn thành tất cả Câu Chuyện Đồng Hành có sẵn</t>
+          <t>Tất cả Câu Chuyện Đồng Hành hiện có đã hoàn thành.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Nhiệm Vụ Người Quay Trở Lại</t>
+          <t>Nhiệm Vụ Người Trở Về</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Etude</t>
+          <t>Khúc Tấu</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Impromptu</t>
+          <t>Ứng Tác</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Đi thôi</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Đã hoàn thành</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Coming Soon</t>
+          <t>Sắp ra mắt</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Đã thất bại</t>
+          <t>Đã đánh bại</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Sẽ có thêm nhiệm vụ trong tương lai</t>
+          <t>Sẽ còn nhiều nhiệm vụ phía trước</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Được đề xuất: Sổ tay - Recurring Challenges</t>
+          <t>Gợi ý: Sổ Tay Hướng Dẫn - Thử Thách Định Kỳ</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Vui lòng kiểm tra Tiến Độ Khám Phá của bạn</t>
+          <t>Hãy kiểm tra Tiến Độ Thám Hiểm của bạn</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Claimable</t>
+          <t>Có thể nhận</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Claimed</t>
+          <t>Đã nhận</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Bạn sẽ mất tiến độ hiện tại nếu thoát giữa chừng</t>
+          <t>Nếu thoát giữa chừng, tiến trình hiện tại sẽ bị mất.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Quit</t>
+          <t>Thoát</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Sắp xếp mặc định</t>
+          <t>Sắp xếp theo Mặc Định</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Không phát hiện vật phẩm sưu tầm đặc biệt trong phạm vi</t>
+          <t>Không phát hiện vật phẩm đặc biệt nào trong phạm vi quét.</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Dream Fragment</t>
+          <t>Mảnh Giấc Mơ</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Đã hoàn thành</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Chưa hoàn thành</t>
+          <t>Chưa Hoàn Tất</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Tổng điểm</t>
+          <t>Tổng Điểm</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Hidden Blade</t>
+          <t>Lưỡi Kiếm Ẩn</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Thunder Cluster</t>
+          <t>Quần Đạn Sấm Sét</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Thrilling Crack</t>
+          <t>Vết Nứt Kinh Hoàng</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Empyreal Illumination</t>
+          <t>Ánh Sáng Siêu Phàm</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Lightning Juggernaut</t>
+          <t>Thiên Lôi Hùng Tráng</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Zeal</t>
+          <t>Nhiệt Huyết</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Berserk</t>
+          <t>Cuồng Nộ</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Unforgotten</t>
+          <t>Không Thể Quên</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Unforgiven</t>
+          <t>Không Thể Tha Thứ</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>5-Star Resonator</t>
+          <t>Resonator 5 Sao</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>5-Star Weapon</t>
+          <t>Vũ Khí 5 Sao</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>4-Star Resonator</t>
+          <t>Resonator 4 Sao</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>4-Star Weapon</t>
+          <t>Vũ Khí 4 Sao</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>3-Star Weapon</t>
+          <t>Vũ Khí 3 Sao</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Data Recording Summary:
+          <t xml:space="preserve">Tóm tắt Ghi chép Dữ liệu:
 </t>
         </is>
       </c>
@@ -3797,7 +3797,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Phân tích hệ thống chỉ ra các lý do sau:
+          <t xml:space="preserve">Phân tích của hệ thống chỉ ra các nguyên nhân sau:
 </t>
         </is>
       </c>
@@ -3868,7 +3868,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Reconfiguration</t>
+          <t>Tái Cấu Trúc</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Tarnish</t>
+          <t>Vết Nhơ</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Repository</t>
+          <t>Kho dữ liệu</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4078,7 +4078,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Đệ tử</t>
+          <t>Đệ Tử</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Pacifism</t>
+          <t>Chủ nghĩa hòa bình</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Saturation</t>
+          <t>Bão Hòa</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Không xương</t>
+          <t>Không Xương</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Outlining</t>
+          <t>Đang Vẽ Đường Viền</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4498,7 +4498,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Splashing</t>
+          <t>Bắn tung tóe</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>"Perfect Alloy"</t>
+          <t>"Hợp Kim Hoàn Hảo"</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4638,7 +4638,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Serenity of Xiehua Village</t>
+          <t>Bình Yên Của Làng Xiehua</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4708,7 +4708,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Bodhi Blossom</t>
+          <t>Hoa Bồ Đề</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4778,7 +4778,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Sabyr Boar Ride</t>
+          <t>Ngựa Lợn Hoang Sabyr</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4848,7 +4848,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Spicy Grass Cake</t>
+          <t>Bánh Cỏ Cay</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Wings of Bane</t>
+          <t>Đôi Cánh Tai Họa</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Moon Fragment</t>
+          <t>Mảnh Trăng</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Harbinger of War</t>
+          <t>Sứ Giả Chiến Tranh</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Lightning Filaments</t>
+          <t>Sợi Sét</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>December 31</t>
+          <t>Ngày 31 tháng 12</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Nữ</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5478,7 +5478,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Enchanted Brush</t>
+          <t>Cọ Phép Thuật</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Miao Zi</t>
+          <t>Miao Tử</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Shin-Fei Chen</t>
+          <t>Shin-Fei Trần</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5828,7 +5828,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Không xác định</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Nam</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -6108,7 +6108,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Matter Weaver</t>
+          <t>Thợ Dệt Vật Chất</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6458,7 +6458,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Paintbrush Set</t>
+          <t>Bộ Cọ Vẽ</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6528,7 +6528,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Empty Birdcage</t>
+          <t>Lồng chim trống</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6598,7 +6598,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Wish List</t>
+          <t>Danh Sách Nguyện Ước</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Xiangli Yao's ID Card</t>
+          <t>Thẻ ID của Tương Lị Dao</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Beep-Boop</t>
+          <t>Bíp Búp</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6808,7 +6808,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>CSC Lock Puzzle</t>
+          <t>Bài Toán Khóa CSC</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6878,7 +6878,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Prized Possessions</t>
+          <t>Vật Báu Trân Quý</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -7018,7 +7018,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Không More Hesitation</t>
+          <t>Không Còn Do Dự</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Kiến Tạo Thế Giới</t>
+          <t>Hóa Thành Thế Giới</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7158,7 +7158,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Một Tia Sáng</t>
+          <t>Tia Sáng Hy Vọng</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7228,7 +7228,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>An Interview</t>
+          <t>Một Cuộc Phỏng Vấn</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7298,7 +7298,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>A Persuasion</t>
+          <t>Một Lời Thuyết Phục</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>A Question</t>
+          <t>Một Câu Hỏi</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>A Ruin</t>
+          <t>Một Tàn Tích</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7508,7 +7508,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>A Smile</t>
+          <t>Một Nụ Cười</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -16958,7 +16958,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Bản Chất Thật</t>
+          <t>Bản Lĩnh Thật</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17028,7 +17028,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Wooly Nhỏ, Cuộc Phiêu Lưu Lớn</t>
+          <t>Cừu Nhỏ, Đại Phiêu Lưu</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17098,7 +17098,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Những Lối Rẽ Giữa Các Vì Sao</t>
+          <t>Những Ngả Đường Giữa Các Vì Sao</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17168,7 +17168,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>If On a Rainy Night a Family</t>
+          <t>Nếu Một Đêm Mưa Gia Đình</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17238,7 +17238,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Starry is the Night</t>
+          <t>Đêm Ngàn Sao</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -17308,7 +17308,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Ngày Ra Khơi, Thuyền Trưởng!</t>
+          <t>Ngày Hành Trình, Thuyền trưởng!</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -17378,7 +17378,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Giấc Mơ Đêm Thoáng Qua</t>
+          <t>Giấc Mộng Đêm Thoáng Qua</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -18079,7 +18079,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;&lt;&lt; [Thông báo Hệ thống] Từ Nghiên cứu viên, Pascar:
+          <t xml:space="preserve">&lt;&lt;&lt; [Thông báo Hệ thống] Từ Nghiên cứu Viên Pascar:
 </t>
         </is>
       </c>
@@ -18295,7 +18295,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;&lt;&lt; Thông báo hệ thống, Nhà nghiên cứu: Pascar
+          <t xml:space="preserve">&lt;&lt;&lt; Tin nhắn hệ thống, Nhà nghiên cứu: Pascar
 </t>
         </is>
       </c>
@@ -18366,7 +18366,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>&lt;&lt;&lt; Từ khóa tìm thấy: Lời nguyện, hiệu chỉnh lại môi trường hình ảnh…</t>
+          <t>&lt;&lt;&lt; Tìm thấy từ khóa: Điều ước, hiệu chỉnh môi trường trực quan…</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -18436,7 +18436,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Complete</t>
+          <t>Hoàn tất</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -18506,7 +18506,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Wonderland Phantasm</t>
+          <t>Ảo Ảnh Kỳ Diệu</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -18576,7 +18576,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Gearworks</t>
+          <t>Xưởng Cơ Khí</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -18646,7 +18646,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Spirited Palettes</t>
+          <t>Bảng Màu Tinh Anh</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -18716,7 +18716,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Blistering Gemstone</t>
+          <t>Đá Quý Rực Lửa</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -18786,7 +18786,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Azure Tranquility</t>
+          <t>Thanh Bình Lam</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -18926,7 +18926,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Aftersound Conch</t>
+          <t>Ốc Dư Âm</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -18996,7 +18996,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Spectrum of Extremity</t>
+          <t>Phổ Cực Đoan</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19066,7 +19066,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Spectrum of Assertion</t>
+          <t>Phổ Khẳng Định</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19136,7 +19136,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>"Nightmare" Incursion</t>
+          <t>"Cuộc Xâm Lăng Của Ác Mộng"</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -19206,7 +19206,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Gearworks of the Unthinkable</t>
+          <t>Xưởng Cơ Khí Vô Tưởng</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -19276,7 +19276,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm vụ Hướng dẫn Sự kiện "Moonlit Reunion" By Moon's Grace</t>
+          <t>Hoàn thành Nhiệm Vụ Hướng Dẫn Sự Kiện Ân Điển Của Ánh Trăng: "Hội Ngộ Dưới Trăng"</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -19346,7 +19346,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Burst Enhancement</t>
+          <t>Tăng Cường Kích Hoạt</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -19416,7 +19416,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Nagetive Status Boost</t>
+          <t>Tăng cường trạng thái tiêu cực</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -19486,7 +19486,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Echo Master</t>
+          <t>Bậc Thầy Echo</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -19556,7 +19556,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Off-Tune Enhancement</t>
+          <t>Tăng Cường Lệch Tần</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -19626,7 +19626,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Dreamworld Showdown</t>
+          <t>Đọ Sức Mộng Ảo</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -19696,7 +19696,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>HP Increase II</t>
+          <t>Tăng HP II</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -19766,7 +19766,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>DMG Up</t>
+          <t>Tăng Sát Thương</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -19836,7 +19836,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Dodge Recovery</t>
+          <t>Phục hồi né tránh</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -19906,7 +19906,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Insufficient Dream Fragments</t>
+          <t>Mảnh Giấc Mơ không đủ</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -20046,7 +20046,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Early Access Available</t>
+          <t>Truy Cập Sớm Đã Mở</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Cyclone Swarm</t>
+          <t>Bầy Xoáy Lốc</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -20326,7 +20326,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Blazing Cutlass</t>
+          <t>Dao Lửa Blaze</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -20396,7 +20396,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Alptop Champion</t>
+          <t>Nhà Vô Địch Alptop</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -20466,7 +20466,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Tambourine Duo</t>
+          <t>Bộ Đôi Tambourine</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -20746,7 +20746,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Phần Thưởng Cấp Tiến</t>
+          <t>Phần Thưởng Cấp Tiếp Theo</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -20816,7 +20816,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Phần Thưởng Có Thể Nhận</t>
+          <t>Phần thưởng có thể nhận</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
@@ -20886,7 +20886,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Cấp Tiên Phong</t>
+          <t>Cấp Độ Tiên Phong</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
@@ -21026,7 +21026,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Trèo lên Mỏ Neo và mở Rương Vật Tư</t>
+          <t>Trèo lên Neo và mở Rương Vật Tư</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -21096,7 +21096,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Complete Yhoran's Tactical Trial I</t>
+          <t>Hoàn thành Thử Thách Chiến Thuật I của Yhoran</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -21166,7 +21166,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Tìm Shorekeeper tại Tethys' Deep: Eidoscope</t>
+          <t>Tìm Shorekeeper ở Tethys' Deep: Eidoscope</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
@@ -21236,7 +21236,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Đạt Cấp Độ Trung Tâm Dữ Liệu 3</t>
+          <t>Đạt Cấp Trung Tâm Dữ Liệu 3.</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -21306,7 +21306,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Complete Yhoran's Tactical Trial II</t>
+          <t>Hoàn thành Thử Thách Chiến Thuật II của Yhoran</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -21446,7 +21446,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Mở khóa sau khi đến Bãi Đen trong Nhiệm Vụ Chính: To the Shore's End</t>
+          <t>Mở khóa sau khi đến Bờ Biển Đen trong Nhiệm Vụ Chính: Đến Tận Cùng Bờ Vực</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
@@ -21586,7 +21586,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ "Hidden Between the Waves" để mở khóa</t>
+          <t>Hoàn thành Nhiệm vụ "Ẩn giấu giữa sóng" để mở khóa</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -21656,7 +21656,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ "Beyond the Shore's End" để mở khóa</t>
+          <t>Hoàn thành Nhiệm vụ "Bên kia bờ vực" để mở khóa</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -21726,7 +21726,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Mở khóa sau khi đến Bãi Đen trong Nhiệm Vụ Chính: To the Shore's End</t>
+          <t>Mở khóa sau khi đến Bờ Biển Đen trong Nhiệm Vụ Chính: Đến Tận Cùng Bờ Vực</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -21796,7 +21796,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Seaside Wandering</t>
+          <t>Dạo Biển Bên Bờ</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -21936,7 +21936,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Cuộc Phiêu Lưu Suốt Đời</t>
+          <t>Hành Trình Phiêu Lưu Suốt Đời</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -22006,7 +22006,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>To the Shore's End</t>
+          <t>Đến Bến Cuối Bờ</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
@@ -22146,7 +22146,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Black Shores: Surface</t>
+          <t>Bờ Biển Đen: Bề Mặt</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -22216,7 +22216,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Black Shores: Archipelago</t>
+          <t>Bờ Đen: Quần Đảo</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -22286,7 +22286,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Black Shores: Underground</t>
+          <t>Bờ Biển Đen: Dưới Lòng Đất</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -22356,7 +22356,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Black Shores: Subterranean Galaxy</t>
+          <t>Bờ Đen: Thiên Hà Ngầm</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -22566,7 +22566,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Thử thách Chiến thuật của Yhoran</t>
+          <t>Thử Thách Chiến Thuật Yhoran</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -22706,7 +22706,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Dream Patrol: Ragunna</t>
+          <t>Tuần Tra Giấc Mộng: Ragunna</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -22776,7 +22776,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Hoàn thành thử thách Nút Mộng Cảnh để nhận thưởng</t>
+          <t>Hoàn thành thử thách Nút Giấc Mơ để nhận phần thưởng.</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -22846,7 +22846,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Dream Patrol: Ragunna</t>
+          <t>Tuần Tra Giấc Mộng: Ragunna</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -22916,7 +22916,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Đánh bại Talons of Delirium</t>
+          <t>Tiêu diệt bọn Talons of Delirium</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -22986,7 +22986,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Dream Patrol: Ragunna</t>
+          <t>Tuần Tra Giấc Mộng: Ragunna</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -23056,7 +23056,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Đánh bại Tongue of Insatiability</t>
+          <t>Hạ gục Tongue of Insatiability</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -23126,7 +23126,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Dream Patrol: Ragunna</t>
+          <t>Tuần Tra Giấc Mộng: Ragunna</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -23196,7 +23196,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Đánh bại Eyes of Resentment</t>
+          <t>Tiêu diệt Mắt Oán Hận</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -23266,7 +23266,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Dream Patrol: Ragunna</t>
+          <t>Tuần Tra Giấc Mộng: Ragunna</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -23336,7 +23336,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Đánh bại Fangs of Cruelty</t>
+          <t>Hạ gục Nanh Độc Ác.</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -23406,7 +23406,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Dream Patrol: Ragunna</t>
+          <t>Tuần Tra Giấc Mộng: Ragunna</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -23476,7 +23476,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Đánh bại Face of Lust</t>
+          <t>Tiêu diệt Bộ Mặt Dục Vọng</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
@@ -23546,7 +23546,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Dream Patrol: Ragunna</t>
+          <t>Tuần Tra Giấc Mộng: Ragunna</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -23616,7 +23616,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Đánh bại Wings of Exhaustion</t>
+          <t>Hạ gục Wings of Exhaustion</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -23686,7 +23686,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Dream Patrol: Ragunna</t>
+          <t>Tuần Tra Giấc Mộng: Ragunna</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
@@ -23756,7 +23756,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Đánh bại Spear of Transgression</t>
+          <t>Đánh bại Ngọn Giáo Phản Nghịch</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -23896,7 +23896,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Dream Contagion: Septimont</t>
+          <t>Ác Mộng Truyền Nhiễm: Septimont</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -23966,7 +23966,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Hoàn thành Dreamscape Node để nhận thưởng</t>
+          <t>Hoàn thành Nút Giấc Mơ để nhận phần thưởng.</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -24036,7 +24036,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Nightmares: Septimont</t>
+          <t>Ác Mộng: Septimont</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
@@ -24106,7 +24106,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Đánh bại Forsworn</t>
+          <t>Hạ gục Những Kẻ Phản Bội.</t>
         </is>
       </c>
       <c r="N338" t="inlineStr">
@@ -24246,7 +24246,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Đánh bại Claws of Regret</t>
+          <t>Hạ gục Claws of Regret</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -24316,7 +24316,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Rush Hour Train</t>
+          <t>Chuyến Tàu Giờ Cao Điểm</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -24386,7 +24386,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Discount Bread</t>
+          <t>Bánh mì giảm giá</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -24456,7 +24456,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Dream-Waking Alarm</t>
+          <t>Báo Thức Tỉnh Mộng</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
@@ -24526,7 +24526,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Friendly Greetings</t>
+          <t>Lời Chào Thân Thiện</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -24596,7 +24596,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Shattered Resolve</t>
+          <t>Ý Chí Tan Rã</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
@@ -24666,7 +24666,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Ý Chí Kiên Trì</t>
+          <t>Ý Chí Kiên Định</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
@@ -24736,7 +24736,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Tai Nghe Đi Làm</t>
+          <t>Tai Nghe Di Chuyển</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -24876,7 +24876,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Payday</t>
+          <t>Ngày lĩnh lương</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
@@ -24946,7 +24946,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>The Black Shores</t>
+          <t>Bờ Biển Đen</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -25016,7 +25016,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Không Tìm Thấy Súng KU-Cass Trong Ba Lô</t>
+          <t>Không tìm thấy Đạn KU-Cass nào trong Ba Lô</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
@@ -25086,7 +25086,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Thời Gian Thử Thách:</t>
+          <t>Thời gian thử thách:</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
@@ -25156,7 +25156,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Thử thách thất bại</t>
+          <t>Thử thách Thất bại</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
@@ -33696,7 +33696,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Shattered Dim Star</t>
+          <t>Ngôi Sao Mờ Vỡ Nát</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -33766,8 +33766,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Đồng Hồ Cát Vòng Luân Hồi
-NAME_TITLE_004441:::Vượt Qua Giá Trị Của Sự Sống</t>
+          <t>Đồng Hồ Vòng Luân Hồi</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -33837,7 +33836,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>"We Are One"</t>
+          <t>"Chúng Ta Là Một"</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -33907,7 +33906,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Master Youhu's Poetry Collection</t>
+          <t>Tập Thơ Của Sư Phụ Hữu Hồ</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -33977,7 +33976,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>An Ice Mask</t>
+          <t>Mặt Nạ Băng</t>
         </is>
       </c>
       <c r="N479" t="inlineStr">
@@ -34047,7 +34046,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>The Ruyi Ring</t>
+          <t>Nhẫn Như Ý</t>
         </is>
       </c>
       <c r="N480" t="inlineStr">
@@ -34117,7 +34116,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Tang YaJing</t>
+          <t>Đường Á Tịnh</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -34677,7 +34676,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>February 27</t>
+          <t>Ngày 27 tháng 2</t>
         </is>
       </c>
       <c r="N489" t="inlineStr">
@@ -34747,7 +34746,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Nữ</t>
         </is>
       </c>
       <c r="N490" t="inlineStr">
@@ -34817,7 +34816,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>The Black Shores</t>
+          <t>Bờ Biển Đen</t>
         </is>
       </c>
       <c r="N491" t="inlineStr">
@@ -34887,7 +34886,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>The Black Shores</t>
+          <t>Bờ Biển Đen</t>
         </is>
       </c>
       <c r="N492" t="inlineStr">
@@ -35027,7 +35026,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>October 13</t>
+          <t>Ngày 13 tháng Mười</t>
         </is>
       </c>
       <c r="N494" t="inlineStr">
@@ -35097,7 +35096,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Nữ</t>
         </is>
       </c>
       <c r="N495" t="inlineStr">
@@ -35237,7 +35236,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Chongzhou</t>
+          <t>Sùng Châu</t>
         </is>
       </c>
       <c r="N497" t="inlineStr">
@@ -35307,7 +35306,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Cryogenic Wonders</t>
+          <t>Kỳ Quan Đông Lạnh</t>
         </is>
       </c>
       <c r="N498" t="inlineStr">
@@ -35377,7 +35376,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>The Shorekeeper's Birth</t>
+          <t>Sự Ra Đời Của Người Gác Bờ</t>
         </is>
       </c>
       <c r="N499" t="inlineStr">
@@ -35447,7 +35446,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Beyond Value Của Sự Sống</t>
+          <t>Vượt Qua Giá Trị Của Sự Sống</t>
         </is>
       </c>
       <c r="N500" t="inlineStr">
@@ -35517,7 +35516,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Vượt Qua Sự Chờ Đợi Bất Tận</t>
+          <t>Vượt Qua Nỗi Chờ Đợi Vô Tận</t>
         </is>
       </c>
       <c r="N501" t="inlineStr">
